--- a/data/trans_camb/P16A04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,92</t>
+          <t>1,1; 4,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,2</t>
+          <t>-0,46; 2,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,28</t>
+          <t>-0,45; 2,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,01</t>
+          <t>-0,24; 3,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,97</t>
+          <t>-0,89; 2,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,84</t>
+          <t>-0,75; 1,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,2</t>
+          <t>0,75; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,66</t>
+          <t>-0,26; 1,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,74</t>
+          <t>-0,03; 1,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 812,09</t>
+          <t>56,3; 755,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 360,2</t>
+          <t>-35,46; 346,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 373,24</t>
+          <t>-32,92; 328,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 278,7</t>
+          <t>-15,83; 269,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 178,83</t>
+          <t>-41,14; 180,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 175,73</t>
+          <t>-28,71; 198,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,17; 337,98</t>
+          <t>37,7; 319,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 169,29</t>
+          <t>-15,5; 196,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 183,07</t>
+          <t>-4,2; 192,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,09</t>
+          <t>-1,14; 2,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,57</t>
+          <t>-2,03; 0,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,54</t>
+          <t>-2,39; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,95</t>
+          <t>0,67; 3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,53</t>
+          <t>-0,93; 1,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,44</t>
+          <t>-0,25; 2,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,5</t>
+          <t>0,23; 2,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,79</t>
+          <t>-1,11; 0,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,17</t>
+          <t>-1,11; 1,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 107,89</t>
+          <t>-36,0; 124,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 30,12</t>
+          <t>-61,26; 33,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 27,26</t>
+          <t>-71,4; 33,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,71; 311,98</t>
+          <t>20,54; 317,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 112,66</t>
+          <t>-39,56; 148,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 183,14</t>
+          <t>-12,04; 205,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 142,2</t>
+          <t>9,06; 150,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 47,76</t>
+          <t>-40,47; 41,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 64,25</t>
+          <t>-39,02; 57,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,34</t>
+          <t>-0,12; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,08</t>
+          <t>-1,2; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,84</t>
+          <t>-0,33; 2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,56</t>
+          <t>-3,99; -0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,11</t>
+          <t>-3,68; -0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,37</t>
+          <t>-3,27; 0,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,76</t>
+          <t>-1,51; 0,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,08</t>
+          <t>-1,97; 0,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,05</t>
+          <t>-1,31; 1,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 394,81</t>
+          <t>-16,05; 355,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 138,64</t>
+          <t>-65,97; 153,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 331,14</t>
+          <t>-21,5; 321,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,95; -21,52</t>
+          <t>-82,18; -18,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,51; 1,53</t>
+          <t>-75,84; 5,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,65; 11,05</t>
+          <t>-69,29; 11,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 39,64</t>
+          <t>-51,46; 38,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 8,86</t>
+          <t>-63,38; 15,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 51,26</t>
+          <t>-43,97; 51,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,48</t>
+          <t>-1,12; 1,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,5</t>
+          <t>-0,14; 2,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,17</t>
+          <t>-0,33; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,02</t>
+          <t>-0,64; 2,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,18</t>
+          <t>-0,55; 2,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,41</t>
+          <t>0,72; 3,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,3</t>
+          <t>-0,49; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,86</t>
+          <t>-0,1; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,93</t>
+          <t>0,65; 2,83</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 118,07</t>
+          <t>-48,2; 120,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 193,13</t>
+          <t>-9,67; 194,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,74; 156,93</t>
+          <t>-15,38; 180,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 146,84</t>
+          <t>-26,38; 164,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 164,56</t>
+          <t>-25,12; 167,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,31; 337,29</t>
+          <t>24,03; 279,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 88,58</t>
+          <t>-21,42; 88,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 134,07</t>
+          <t>-6,67; 122,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,53; 200,26</t>
+          <t>25,77; 190,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,9</t>
+          <t>0,3; 1,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,92</t>
+          <t>-0,42; 0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,1</t>
+          <t>-0,35; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,35</t>
+          <t>-0,07; 1,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,76</t>
+          <t>-0,67; 0,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,65</t>
+          <t>0,05; 1,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,41</t>
+          <t>0,29; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,63</t>
+          <t>-0,38; 0,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,16</t>
+          <t>0,06; 1,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,46; 130,47</t>
+          <t>12,31; 125,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 60,72</t>
+          <t>-18,72; 61,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 74,33</t>
+          <t>-17,24; 73,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 71,1</t>
+          <t>-4,52; 74,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 39,9</t>
+          <t>-26,01; 41,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,17; 86,98</t>
+          <t>0,54; 87,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,9; 80,93</t>
+          <t>12,99; 78,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 36,03</t>
+          <t>-16,79; 34,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 65,44</t>
+          <t>2,75; 67,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,57</t>
+          <t>0,96; 4,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,1</t>
+          <t>-0,48; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,2</t>
+          <t>-0,33; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,11</t>
+          <t>-0,26; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,04</t>
+          <t>-0,72; 2,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,9</t>
+          <t>-0,58; 1,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,23</t>
+          <t>0,93; 3,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,77</t>
+          <t>-0,26; 1,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,73</t>
+          <t>-0,09; 1,65</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,3; 755,66</t>
+          <t>40,79; 760,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 346,76</t>
+          <t>-42,72; 342,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 328,56</t>
+          <t>-34,59; 388,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 269,9</t>
+          <t>-20,75; 274,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 180,03</t>
+          <t>-35,11; 216,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 198,95</t>
+          <t>-26,02; 189,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,7; 319,77</t>
+          <t>44,32; 321,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 196,35</t>
+          <t>-19,31; 174,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 192,47</t>
+          <t>-9,78; 167,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,37</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,24</t>
+          <t>-1,09; 2,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,52</t>
+          <t>-2,12; 0,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,64</t>
+          <t>-1,76; 1,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,98</t>
+          <t>0,74; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,72</t>
+          <t>-1,07; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,52</t>
+          <t>-0,21; 2,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,57</t>
+          <t>0,24; 2,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,72</t>
+          <t>-1,1; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,05</t>
+          <t>-0,7; 1,26</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-32,21%</t>
+          <t>-14,15%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 124,01</t>
+          <t>-33,87; 126,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 33,7</t>
+          <t>-60,97; 42,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 33,81</t>
+          <t>-54,44; 59,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,54; 317,48</t>
+          <t>23,11; 333,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 148,94</t>
+          <t>-43,08; 123,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 205,44</t>
+          <t>-11,75; 180,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 150,38</t>
+          <t>5,86; 136,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 41,58</t>
+          <t>-39,61; 44,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 57,48</t>
+          <t>-25,98; 72,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,04</t>
+          <t>0,01; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,14</t>
+          <t>-1,24; 1,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,81</t>
+          <t>-0,16; 2,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,64</t>
+          <t>-4,19; -0,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,05</t>
+          <t>-3,57; 0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,46</t>
+          <t>-2,01; 1,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,7</t>
+          <t>-1,59; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,15</t>
+          <t>-1,98; 0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,09</t>
+          <t>-0,91; 1,61</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-36,42%</t>
+          <t>-6,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 355,43</t>
+          <t>-4,98; 373,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 153,63</t>
+          <t>-64,29; 170,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 321,47</t>
+          <t>-15,42; 355,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,18; -18,63</t>
+          <t>-81,56; -17,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,84; 5,0</t>
+          <t>-74,08; 13,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,29; 11,22</t>
+          <t>-44,12; 58,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,46; 38,74</t>
+          <t>-50,43; 34,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 15,65</t>
+          <t>-63,57; 5,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 51,27</t>
+          <t>-27,13; 80,89</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,55</t>
+          <t>-1,13; 1,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,47</t>
+          <t>-0,21; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,25</t>
+          <t>-0,61; 1,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,02</t>
+          <t>-0,49; 2,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,14</t>
+          <t>-0,51; 2,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,87</t>
+          <t>1,1; 3,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,26</t>
+          <t>-0,36; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,79</t>
+          <t>-0,07; 1,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,83</t>
+          <t>0,62; 2,5</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>118,42%</t>
+          <t>127,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 120,15</t>
+          <t>-51,81; 117,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 194,9</t>
+          <t>-12,54; 197,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 180,42</t>
+          <t>-26,67; 166,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 164,13</t>
+          <t>-23,08; 154,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 167,52</t>
+          <t>-23,58; 161,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,03; 279,92</t>
+          <t>40,24; 313,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 88,71</t>
+          <t>-16,73; 97,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 122,85</t>
+          <t>-5,54; 127,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,77; 190,83</t>
+          <t>25,16; 168,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0,14</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,87</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,91</t>
+          <t>-0,4; 0,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,11</t>
+          <t>-0,17; 1,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,48</t>
+          <t>-0,06; 1,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,78</t>
+          <t>-0,74; 0,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,69</t>
+          <t>0,41; 1,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,36</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,62</t>
+          <t>-0,37; 0,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,2</t>
+          <t>0,29; 1,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,31; 125,44</t>
+          <t>13,66; 117,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 61,01</t>
+          <t>-19,8; 61,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 73,09</t>
+          <t>-8,61; 86,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 74,72</t>
+          <t>-2,11; 81,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 41,09</t>
+          <t>-28,23; 42,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,54; 87,84</t>
+          <t>12,82; 101,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,99; 78,01</t>
+          <t>13,56; 81,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 34,41</t>
+          <t>-16,44; 36,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,75; 67,66</t>
+          <t>13,0; 73,98</t>
         </is>
       </c>
     </row>
